--- a/校园招聘/制造业/制造业通用/技术研发类/机械工程师/4_需重新出答案/5轮_制造业通用_机械工程师_重新出答案.xlsx
+++ b/校园招聘/制造业/制造业通用/技术研发类/机械工程师/4_需重新出答案/5轮_制造业通用_机械工程师_重新出答案.xlsx
@@ -526,7 +526,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>制造业通用</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
